--- a/assets/constructions/examples/ctd_tge_face.xlsx
+++ b/assets/constructions/examples/ctd_tge_face.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,11 +624,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QFT-RFG100C16-055B</t>
+          <t>QS-LF123J25C2525E-120B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -638,12 +658,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoroCutⓇ QF QS shank tool for face grooving</t>
+          <t>CoroCutⓇ 1-2 QS shank tool for face grooving</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QFT-G</t>
+          <t>123J2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -652,28 +672,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CoroCut QFT -size G (QFT-G-0300-03-TF)</t>
+          <t>CoroCut 2 -size J (N123J2-0500-0004-TF)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ISO_5610:25.4X25.4</t>
+          <t>ISO_5610:25X25</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>COR_QFT-G</t>
+          <t>COR_R123_J</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -681,14 +701,14 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>35</v>
+        <v>42.821</v>
       </c>
       <c r="P2" t="n">
-        <v>35</v>
+        <v>67.821</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -698,22 +718,22 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="U2" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>119</v>
+        <v>126.821</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="AD2" t="n">
         <v>25</v>
@@ -724,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
@@ -733,7 +753,7 @@
         </is>
       </c>
       <c r="AK2" t="n">
-        <v>0.456</v>
+        <v>0.497</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -743,11 +763,17 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MGFHRL325-44/70-T10</t>
+          <t>MGFHRR425-112/200-T15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -757,12 +783,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MGFHRL</t>
+          <t>MGFHRR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MFMN300</t>
+          <t>DER_MG-400</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -771,20 +797,20 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="H3" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MFMN300*</t>
+          <t>MGMN400</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -794,7 +820,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DER_MFMN300</t>
+          <t>DER_MG-400</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -805,7 +831,7 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -829,16 +855,14 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
         <v>25.6</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="n">
-        <v>3</v>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -857,14 +881,28 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2017/derek Металлорежущий инструмент и оснастка</t>
-        </is>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>77.26000000000001</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6333.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QS-RF123K100C16E-220B</t>
+          <t>QFU-LFH38C2525-150B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -874,12 +912,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CoroCutⓇ 1-2 QS shank tool for face grooving</t>
+          <t>CoroCutⓇ QF QS shank tool for face grooving</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>123K2</t>
+          <t>QFU-H</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -888,28 +926,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25.4</v>
+        <v>38</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CoroCut 2 -size K (N123K2-0600-0004-TF)</t>
+          <t>CoroCut QFU -size H (QFU-H-0400-03-TF)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ISO_5610:25.4X25.4</t>
+          <t>ISO_5610:25X25</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>COR_R123_K</t>
+          <t>COR_QFU-H</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -917,14 +955,14 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>43.221</v>
+        <v>47.6</v>
       </c>
       <c r="P4" t="n">
-        <v>68.621</v>
+        <v>47.6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -934,25 +972,25 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="U4" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>127.221</v>
+        <v>131.6</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -960,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
@@ -969,7 +1007,7 @@
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>0.517</v>
+        <v>0.452</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -979,11 +1017,17 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QFT-RFH32C2525-065B</t>
+          <t>QS-RF123G055C12E-034B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -993,12 +1037,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CoroCutⓇ QF QS shank tool for face grooving</t>
+          <t>CoroCutⓇ 1-2 QS shank tool for face grooving</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>QFT-H</t>
+          <t>123G2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1007,28 +1051,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>13.97</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CoroCut QFT -size H (QFT-H-0400-03-TF)</t>
+          <t>CoroCut 2 -size G (N123G2-0300-0003-TF)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>ISO_5610:19.05X19.05</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>COR_QFT-H</t>
+          <t>COR_R123_G</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -1036,10 +1080,10 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>41.6</v>
+        <v>37.18</v>
       </c>
       <c r="P5" t="n">
-        <v>41.6</v>
+        <v>56.23</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1053,25 +1097,25 @@
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>25</v>
+        <v>19.05</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>19.05</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>125.6</v>
+        <v>100.87</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>25.5</v>
+        <v>19.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>19.05</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -1079,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
@@ -1088,7 +1132,7 @@
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>0.448</v>
+        <v>0.276</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1098,11 +1142,17 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QFGD2525LR13-64H</t>
+          <t>QFFD2525LR10-100H</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1117,7 +1167,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ZT0404</t>
+          <t>ZT0303</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1126,7 +1176,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -1135,7 +1185,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ZTGD0404-MG</t>
+          <t>ZTFD0303-MG</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1145,7 +1195,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>DER_ZT0404W</t>
+          <t>DER_ZT0303W</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -1180,7 +1230,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="n">
         <v>26</v>
@@ -1211,6 +1261,12 @@
           <t>2017/derek Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
+      <c r="AN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
